--- a/ValueSet-i2x-efr.xlsx
+++ b/ValueSet-i2x-efr.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.2</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-i2x-efr.xlsx
+++ b/ValueSet-i2x-efr.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="52">
   <si>
     <t>Property</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>Jeu d'observations d'une épreuve fonctionnelle respiratoire</t>
+    <t>Valueset for pulmonary function test measurements</t>
   </si>
   <si>
     <t>Status</t>
@@ -79,9 +79,6 @@
   </si>
   <si>
     <t>Description</t>
-  </si>
-  <si>
-    <t>Jeu d'bservations d'une épreuve fonctionnelle respiratoire</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -403,29 +400,29 @@
         <v>21</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>24</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>25</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>26</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -444,7 +441,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B1" t="s" s="1">
         <v>21</v>
@@ -452,90 +449,90 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s" s="2">
         <v>29</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
+        <v>30</v>
+      </c>
+      <c r="B3" t="s" s="2">
         <v>31</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
+        <v>32</v>
+      </c>
+      <c r="B4" t="s" s="2">
         <v>33</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
+        <v>34</v>
+      </c>
+      <c r="B5" t="s" s="2">
         <v>35</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
+        <v>36</v>
+      </c>
+      <c r="B6" t="s" s="2">
         <v>37</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s" s="2">
         <v>39</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>40</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s" s="2">
         <v>41</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>42</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s" s="2">
         <v>43</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>44</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
+        <v>44</v>
+      </c>
+      <c r="B10" t="s" s="2">
         <v>45</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>46</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
         <v>47</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s" s="2">
         <v>49</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>50</v>
       </c>
     </row>
     <row r="13">
@@ -548,10 +545,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
+        <v>50</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>51</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>52</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-i2x-efr.xlsx
+++ b/ValueSet-i2x-efr.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.2</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>

--- a/ValueSet-i2x-efr.xlsx
+++ b/ValueSet-i2x-efr.xlsx
@@ -87,7 +87,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>RM@H IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
+    <t>VUNS IG (C) 2025-2025 University Hospital of Liege, GSI Department, Belgium. This implementation guide is free software: you can redistribute it and/or modify it under the terms of the GNU General Public License as published by the Free Software Foundation, either version 3 of the License, or (at your option) any later version. This program is distributed in the hope that it will be useful, but WITHOUT ANY WARRANTY; without even the implied warranty of MERCHANTABILITY or FITNESS FOR A PARTICULAR PURPOSE. See the GNU General Public License for more details. You should have received a copy of the GNU General Public License along with this program. If not, see &lt;http://www.gnu.org/licenses/&gt;.</t>
   </si>
   <si>
     <t>Immutable</t>
